--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_470_Malta.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_470_Malta.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc17f2692688b4219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rddd67cff88fd401b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf06223b3a1e0438b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R064bda9267ed4526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R686899aeba1c4d98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R6a77b02ed2a54fbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf32371e388b34cd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R72d1690b424048ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf5b92364ce354a98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rbe879a78fc4f40be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9a8c1d60fefb4f3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R51e9ac9ccecd473e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ470CommercialTable" displayName="EEZ470CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ470CommercialTable" displayName="EEZ470CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ470FunctionalTable" displayName="EEZ470FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ470FunctionalTable" displayName="EEZ470FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ470ValidationTable" displayName="EEZ470ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ470ValidationTable" displayName="EEZ470ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -14965,7 +14919,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a5409826ecb4c01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79be4ebca9e34770"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14975,20 +14929,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -14996,714 +14940,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.7307336672</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.166906904477714</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>146.86114318219123</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.7307336672</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>147.5817010905409</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$214,A2,'Species'!$U$2:$U$214))</x:f>
-        <x:v>107.84291764950518</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.166906904477714</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>146.86114318219123</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>107.31638172670688</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0.5265359227983026</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.004906389074309</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.004906389074309131</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>192.4067355421</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.8996500574622233</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>793.6884446971025</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>192.4067355421</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>848.5620593476092</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$214,A3,'Species'!$U$2:$U$214))</x:f>
-        <x:v>163269.0557439552</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.8996500574622233</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>793.6884446971025</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>152711.00268165604</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>10558.05306229915</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0691374745558357</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.06913747455583569</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>382.92261337580004</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.378830466976048</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>239.238167391</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>382.92261337580004</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>268.4313552715937</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$214,A4,'Species'!$U$2:$U$214))</x:f>
-        <x:v>102788.4360726065</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.378830466976048</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>239.238167391</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>91609.70427659882</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>11178.73179600769</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1220256290998991</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.12202562909989914</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>16.348062845600005</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.6843956894924905</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>483.4991216889768</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>16.348062845600005</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>522.0281397840538</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$214,A5,'Species'!$U$2:$U$214))</x:f>
-        <x:v>8534.148836361375</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.6843956894924905</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>483.4991216889768</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>7904.274027163797</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>629.8748091975785</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0796878760823516</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.07968787608235156</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>46.4750860016</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0579130452854537</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>114.26495298766575</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>46.4750860016</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>115.97196047215294</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$214,A6,'Species'!$U$2:$U$214))</x:f>
-        <x:v>5389.806836717464</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0579130452854537</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>114.26495298766575</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5310.473517070546</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>79.33331964691752</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0149390293336178</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.014939029333617826</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.605175093</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.221747577076838</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>16.66278447918969</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.605175093</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>25.5536092917544</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$214,A7,'Species'!$U$2:$U$214))</x:f>
-        <x:v>15.464407879623135</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.221747577076838</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>16.66278447918969</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>10.083902146832578</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>5.3805057327905566</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.5335737747594675</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.5335737747594674</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>678.7479246459998</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5592156405447652</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>362.4229078492392</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>678.7479246459998</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>532.738741042351</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$214,A8,'Species'!$U$2:$U$214))</x:f>
-        <x:v>361595.3148610184</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5592156405447652</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>362.4229078492392</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>245993.79654683953</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>115601.51831417886</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.4699367217260995</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.46993672172609946</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2376.8161029934</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.126249313894996</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1337.3630314817422</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2376.8161029934</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1830.2589705443372</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$214,A9,'Species'!$U$2:$U$214))</x:f>
-        <x:v>4350188.993837903</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.126249313894996</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1337.3630314817422</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3178665.988773874</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1171523.0050640292</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.368558070964835</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.3685580709648351</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2.323418335</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.5028571428278754</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>318.31502815114715</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2.323418335</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>318.62399497928016</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$214,A10,'Species'!$U$2:$U$214))</x:f>
-        <x:v>740.2968319058075</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.5028571428278754</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>318.31502815114715</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>739.5789727124164</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0.7178591933910639</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0009706322379046</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0009706322379046351</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>70.6726329488</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.9972655921246636</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>993.7235727643216</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>70.6726329488</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1169.2145886166413</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$214,A11,'Species'!$U$2:$U$214))</x:f>
-        <x:v>82631.47345968608</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.9972655921246636</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>993.7235727643216</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>70229.06131054305</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>12402.412149143027</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1765994293203108</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.17659942932031086</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>233.99447578950003</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.085309718920166</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1217.0536381053746</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>233.99447578950003</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1354.5376731037888</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$214,A12,'Species'!$U$2:$U$214))</x:f>
-        <x:v>316954.3327550502</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.085309718920166</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1217.0536381053746</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>284783.828056171</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>32170.504698879202</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.112964647320261</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.11296464732026097</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3730.9551272451</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.469532197615017</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2948.0320289616734</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3730.9551272451</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2962.9943048730834</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$214,A13,'Species'!$U$2:$U$214))</x:f>
-        <x:v>11054798.793764262</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.469532197615017</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2948.0320289616734</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>10998975.21373733</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>55823.58002693206</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0050753437426798</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.005075343742679808</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17990d35dd4b4556"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6934fcf1eb614808"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15713,20 +15193,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -15734,1416 +15204,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>165.559567826</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.858136205735429</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>721.3336721975629</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>165.559567826</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>847.6166132787421</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$214,A2,'Species'!$U$2:$U$214))</x:f>
-        <x:v>140331.0401765663</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.858136205735429</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>721.3336721975629</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>119423.69102737008</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>20907.349149196234</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1750686900508258</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.17506869005082576</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>147.56160706810002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.8429163229427243</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>696.4923055405927</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>147.56160706810002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>738.155814858384</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$214,A3,'Species'!$U$2:$U$214))</x:f>
-        <x:v>108923.45830716605</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.8429163229427243</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>696.4923055405927</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>102775.52391613601</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>6147.934391030038</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0598190518206134</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.05981905182061346</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>10.9568148255</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.1503403252911895</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1413.6448823259318</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>10.9568148255</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1818.2616291578006</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$214,A4,'Species'!$U$2:$U$214))</x:f>
-        <x:v>19922.355974993974</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.1503403252911895</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1413.6448823259318</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>15489.045204660973</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>4433.310770333001</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2862223404835131</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.2862223404835132</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>25.089315940700004</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.213202031281916</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1633.811810946528</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>25.089315940700004</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1774.2893062695948</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$214,A5,'Species'!$U$2:$U$214))</x:f>
-        <x:v>44515.7049752033</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.213202031281916</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1633.811810946528</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>40991.22071248467</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>3524.48426271863</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0859814419150777</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.08598144191507769</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.043431715</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.043431715</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$214,A6,'Species'!$U$2:$U$214))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>99.49631099772897</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>99.49631099772897</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3834.9746269847997</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.4550785912828195</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2851.5342433389987</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3834.9746269847997</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2869.322007448776</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$214,A7,'Species'!$U$2:$U$214))</x:f>
-        <x:v>11003777.095215145</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.4550785912828195</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2851.5342433389987</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>10935561.47118336</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>68215.62403178588</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0062379626516245</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.006237962651624519</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>38.0399862662</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7790353386082156</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>601.2226570722369</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>38.0399862662</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>700.5857226493822</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$214,A8,'Species'!$U$2:$U$214))</x:f>
-        <x:v>26650.271267878303</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7790353386082156</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>601.2226570722369</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>22870.501617956164</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>3779.7696499221383</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1652683318040804</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.16526833180408046</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>23.688031261200003</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.257396415966319</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1808.8244341815955</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>23.688031261200003</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2192.5970689737337</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$214,A9,'Species'!$U$2:$U$214))</x:f>
-        <x:v>51938.307913065306</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.257396415966319</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1808.8244341815955</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>42847.48974291604</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>9090.818170149265</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2121668789628977</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.21216687896289763</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>47.6051128632</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.1430737926159</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1390.1888233808368</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>47.6051128632</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1693.5935531349082</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$214,A10,'Species'!$U$2:$U$214))</x:f>
-        <x:v>80623.71224137521</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.1430737926159</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1390.1888233808368</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>66180.09583820394</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>14443.616403171269</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.2182471363970642</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.21824713639706408</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>19.830380283600004</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.9846007167377646</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>96.51631157304325</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>19.830380283600004</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>112.46221411111438</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$214,A11,'Species'!$U$2:$U$214))</x:f>
-        <x:v>2230.1684733590446</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.9846007167377646</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>96.51631157304325</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1913.9551620638717</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>316.21331129517284</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1652145868214547</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.16521458682145465</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>20.6656508696</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.931452037798438</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>853.9885302362776</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>20.6656508696</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1481.7471620015037</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$214,A12,'Species'!$U$2:$U$214))</x:f>
-        <x:v>30621.269526943706</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.931452037798438</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>853.9885302362776</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>17648.228812505757</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>12973.04071443795</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.7350902377945763</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.7350902377945763</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>242.64432898670003</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.744805887150665</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>555.6558450707654</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>242.64432898670003</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>687.3248295845378</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$214,A13,'Species'!$U$2:$U$214))</x:f>
-        <x:v>166775.47207043815</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.744805887150665</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>555.6558450707654</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>134826.73967473363</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>31948.732395704516</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2369613955865142</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.23696139558651413</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>581.2487899915</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.408969075333783</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>256.430143463658</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>581.2487899915</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>383.51645353045603</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$214,A14,'Species'!$U$2:$U$214))</x:f>
-        <x:v>222918.47455640888</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.408969075333783</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>256.430143463658</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>149049.71060559797</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>73868.76395081091</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.4955981709100787</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.49559817091007874</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1788.0974957280005</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.2848350708652045</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>1926.7930488160139</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1788.0974957280005</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>2303.546598356408</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$214,A15,'Species'!$U$2:$U$214))</x:f>
-        <x:v>4118965.9038138473</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.2848350708652045</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>1926.7930488160139</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>3445293.8253740333</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>673672.078439814</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.19553399871974</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.19553399871973992</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>59.50119312329999</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.600843222157513</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>398.88088263436094</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>59.50119312329999</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>620.4390655292895</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$214,A16,'Species'!$U$2:$U$214))</x:f>
-        <x:v>36916.86465929803</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.600843222157513</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>398.88088263436094</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>23733.88843081947</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>13182.976228478561</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.5554494901627625</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.5554494901627625</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>0.7025845086000001</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.249131634235409</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>17.747273175023906</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>0.7025845086000001</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>25.753935091778395</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$214,A17,'Species'!$U$2:$U$214))</x:f>
-        <x:v>18.09431583097342</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.249131634235409</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>17.747273175023906</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>12.468959202664134</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>5.625356628309287</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.451148851871082</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.45114885187108206</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>363.09223309220005</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.400361431160426</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>251.39777588200863</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>363.09223309220005</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>276.9496520012663</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$214,A18,'Species'!$U$2:$U$214))</x:f>
-        <x:v>100558.26759924747</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.400361431160426</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>251.39777588200863</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>91280.57983941094</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>9277.687759836524</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.101639229025042</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.10163922902504205</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>2.2680988514</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>316.22776601683796</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>2.2680988514</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$214,A19,'Species'!$U$2:$U$214))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>717.2358328835782</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.5</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>316.22776601683796</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>717.2358328835782</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>6.063879482100001</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.416182886878553</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>260.72512652116444</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>6.063879482100001</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>267.24764945464176</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$214,A20,'Species'!$U$2:$U$214))</x:f>
-        <x:v>1620.5575381674557</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.416182886878553</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>260.72512652116444</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1581.0057451796158</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>39.55179298783992</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0250168559528836</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.025016855952883648</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>142.5207524063</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.62174810668863</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>418.55073285680345</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>142.5207524063</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>451.68556906934936</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$214,A21,'Species'!$U$2:$U$214))</x:f>
-        <x:v>64374.56715483146</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.62174810668863</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>418.55073285680345</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>59652.1653669599</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>4722.401787871553</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0791656389809312</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.07916563898093117</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>45.205819668800004</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.0644491854365556</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>115.99764853256559</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>45.205819668800004</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>117.67068058300346</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$214,A22,'Species'!$U$2:$U$214))</x:f>
-        <x:v>5319.3995667402205</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.0644491854365556</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>115.99764853256559</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>5243.768781568004</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>75.63078517221675</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0144229824621676</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.014422982462167498</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>2.9843789496</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.4449725904258877</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>278.5945334056598</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>2.9843789496</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>362.30019099620176</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$214,A23,'Species'!$U$2:$U$214))</x:f>
-        <x:v>1081.241063445124</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.4449725904258877</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>278.5945334056598</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>831.431660969485</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>249.80940247563888</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.3004569277339648</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.30045692773396476</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>16.304631130600004</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.6825960379927603</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>481.4997189816776</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>16.304631130600004</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>517.3163659945525</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$214,A24,'Species'!$U$2:$U$214))</x:f>
-        <x:v>8434.652525363646</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.6825960379927603</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>481.4997189816776</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>7850.675307483814</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>583.9772178798321</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0743856031497245</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.07438560314972446</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>0.4436159559999999</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.5722764044582744</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>373.487786523008</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>0.4436159559999999</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>400.363170512145</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$214,A25,'Species'!$U$2:$U$214))</x:f>
-        <x:v>177.60749063393618</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.5722764044582744</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>373.487786523008</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>165.6851414727281</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>11.922349161208075</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0719578657158615</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.07195786571586145</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>147.90576070410003</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>4.147027380854572</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>1402.9021501915552</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>147.90576070410003</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>1416.4610002871584</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$214,A26,'Species'!$U$2:$U$214))</x:f>
-        <x:v>209502.74175516263</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>4.147027380854572</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>1402.9021501915552</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>207497.30971749956</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>2005.432037663064</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.0096648580186094</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.00966485801860945</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf743cd56873346c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dc74c6e240345f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17318,7 +15869,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -17417,7 +15968,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>16447013.960324993</x:v>
+        <x:v>15037040.322183833</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -17431,7 +15982,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>16447013.960324995</x:v>
+        <x:v>15493537.20996647</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -17445,7 +15996,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1409973.6381411608</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -17459,7 +16010,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.862645149230957e-9</x:v>
+        <x:v>-953476.7503585238</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -17470,9 +16021,9 @@
         <x:v>EEZ_470</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -17484,47 +16035,19 @@
         <x:v>EEZ_470</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_470</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_470</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5b2471cc8aa454d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69fe5386b8504436"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17571,7 +16094,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
